--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N65_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N65_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.99522851950456</v>
+        <v>9.586724634419491</v>
       </c>
       <c r="D2" t="n">
-        <v>59.2277492894927</v>
+        <v>9.624509259542563</v>
       </c>
       <c r="E2" t="n">
-        <v>11.85996788815557</v>
+        <v>1.927244781825279</v>
       </c>
       <c r="F2" t="n">
-        <v>11.91927205672646</v>
+        <v>1.93688170921805</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.32022971565521</v>
+        <v>10.12703732879397</v>
       </c>
       <c r="D3" t="n">
-        <v>62.59185583766195</v>
+        <v>10.17117657362007</v>
       </c>
       <c r="E3" t="n">
-        <v>11.85996788815557</v>
+        <v>1.927244781825279</v>
       </c>
       <c r="F3" t="n">
-        <v>11.91927205672646</v>
+        <v>1.93688170921805</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.47099853809939</v>
+        <v>8.68903726244115</v>
       </c>
       <c r="D4" t="n">
-        <v>53.62548083617455</v>
+        <v>8.714140635878364</v>
       </c>
       <c r="E4" t="n">
-        <v>11.85996788815557</v>
+        <v>1.927244781825279</v>
       </c>
       <c r="F4" t="n">
-        <v>11.91927205672646</v>
+        <v>1.93688170921805</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>80.82269013393818</v>
+        <v>13.13368714676495</v>
       </c>
       <c r="D5" t="n">
-        <v>80.83166847665832</v>
+        <v>13.13514612745698</v>
       </c>
       <c r="E5" t="n">
-        <v>11.85996788815557</v>
+        <v>1.927244781825279</v>
       </c>
       <c r="F5" t="n">
-        <v>11.91927205672646</v>
+        <v>1.93688170921805</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.14061562025575</v>
+        <v>7.33535003829156</v>
       </c>
       <c r="D6" t="n">
-        <v>44.87702153421648</v>
+        <v>7.292515999310178</v>
       </c>
       <c r="E6" t="n">
-        <v>11.85996788815557</v>
+        <v>1.927244781825279</v>
       </c>
       <c r="F6" t="n">
-        <v>11.91927205672646</v>
+        <v>1.93688170921805</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
